--- a/pensum/ok09/OK09_Budsjettering_Regneark_Delbudsjetter.xlsx
+++ b/pensum/ok09/OK09_Budsjettering_Regneark_Delbudsjetter.xlsx
@@ -1980,7 +1980,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2079,6 +2079,10 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2587,8 +2591,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
+    <row ht="27" customHeight="true" r="39" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="25" r="A39" t="s">
         <v>53</v>
       </c>
       <c r="B39" s="9" t="s">
@@ -3346,7 +3350,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
         <v>115</v>
       </c>
@@ -3686,8 +3690,8 @@
         <v>543</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
+    <row ht="27" customHeight="true" r="29" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="25" r="A29" t="s">
         <v>544</v>
       </c>
       <c r="B29" s="20" t="str">
@@ -3695,8 +3699,8 @@
         <v>OK — bedriften solgte mer enn planlagt. Da MÅ varekostnaden og lønnskostnaden også være høyere</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
+    <row ht="27" customHeight="true" r="30" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="25" r="A30" t="s">
         <v>545</v>
       </c>
       <c r="B30" s="20" t="str">
@@ -3704,8 +3708,8 @@
         <v>OK — varekostnaden utgjør nesten nøyaktig samme andel av salget som budsjettert. Materiellbudsjettet har holdt</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
+    <row ht="27" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="25" r="A31" t="s">
         <v>546</v>
       </c>
       <c r="B31" s="20" t="str">
@@ -7459,8 +7463,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
+    <row ht="27" customHeight="true" r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="25" r="A27" t="s">
         <v>289</v>
       </c>
       <c r="B27" s="11" t="n">
@@ -8304,7 +8308,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="52.5" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
         <v>318</v>
       </c>
